--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487126_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487126_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>A. MASSALEY JR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9754</v>
+        <v>0.5863</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5027</v>
+        <v>2.3683</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.5273</v>
+        <v>-1.7821</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6838</v>
+        <v>0.3577</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4263</v>
+        <v>0.1449</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7426</v>
+        <v>0.2128</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6165</v>
+        <v>4.5431</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5001</v>
+        <v>3.3635</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1164</v>
+        <v>1.1796</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.3003</v>
+        <v>-4.1854</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.9265</v>
+        <v>-3.2186</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3738</v>
+        <v>-0.9668</v>
       </c>
       <c r="P2" t="n">
-        <v>0.772</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7021</v>
+        <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8871</v>
+        <v>0.0658</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3604</v>
+        <v>-0.1143</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5268</v>
+        <v>0.1801</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4559</v>
+        <v>1.7997</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2375</v>
+        <v>-0.3317</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7003</v>
+        <v>0.6596</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9377</v>
+        <v>-0.9913</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0803</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1343</v>
+        <v>-1.2284</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3146</v>
+        <v>-0.3552</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8197</v>
+        <v>-0.8732</v>
       </c>
       <c r="V3" t="n">
         <v>1.5561</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MASSALEY JR</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2734</v>
+        <v>-0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>1.589</v>
+        <v>0.3118</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8624</v>
+        <v>-0.9518</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3577</v>
+        <v>-1.9259</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1449</v>
+        <v>-2.8669</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2128</v>
+        <v>0.9411</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5431</v>
+        <v>1.1447</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3635</v>
+        <v>-0.8903</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1796</v>
+        <v>2.035</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.1854</v>
+        <v>-3.0705</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.2186</v>
+        <v>-1.9767</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9668</v>
+        <v>-1.0939</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3511</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7938</v>
+        <v>-0.9687</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.1537</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0998</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5138</v>
+        <v>2.2546</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7997</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>1.9687</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6192</v>
+        <v>-0.6566</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4933</v>
+        <v>4.3794</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1125</v>
+        <v>-5.0359</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9259</v>
+        <v>-1.6838</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8669</v>
+        <v>-2.4263</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9411</v>
+        <v>0.7426</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1447</v>
+        <v>3.6165</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8903</v>
+        <v>1.5001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.035</v>
+        <v>2.1164</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0705</v>
+        <v>-5.3003</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9767</v>
+        <v>-3.9265</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0939</v>
+        <v>-1.3738</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>2.7021</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9478</v>
+        <v>0.2552</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0278</v>
+        <v>0.237</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9756</v>
+        <v>0.0181</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2546</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>2.4559</v>
       </c>
       <c r="X5" t="n">
-        <v>1.9687</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5496</v>
+        <v>-0.7752</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5194</v>
+        <v>1.0796</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.069</v>
+        <v>-1.8548</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7187</v>
@@ -922,13 +922,13 @@
         <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0311</v>
+        <v>-0.2568</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7892</v>
+        <v>-0.229</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2419</v>
+        <v>-0.0278</v>
       </c>
       <c r="V6" t="n">
         <v>0.6562</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0961</v>
+        <v>-1.9433</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2657</v>
+        <v>0.6314</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8304</v>
+        <v>-2.5747</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8381</v>
+        <v>-2.3731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4904</v>
+        <v>-0.7038</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3477</v>
+        <v>-1.6693</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1296</v>
+        <v>0.9313</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1242</v>
+        <v>1.6402</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2538</v>
+        <v>-0.709</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7085</v>
+        <v>-3.3044</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6146</v>
+        <v>-2.344</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0939</v>
+        <v>-0.9604</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5441</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.3772</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.5628</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.8144</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.7371</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.7092000000000001</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.1361</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.5731000000000001</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.2859</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5768</v>
+        <v>-2.3777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.212</v>
+        <v>-1.3064</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7888</v>
+        <v>-1.0713</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3731</v>
+        <v>-2.8381</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7038</v>
+        <v>-0.4904</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6693</v>
+        <v>-2.3477</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9313</v>
+        <v>-1.1296</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6402</v>
+        <v>0.1242</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.709</v>
+        <v>-1.2538</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3044</v>
+        <v>-1.7085</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.344</v>
+        <v>-0.6146</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9604</v>
+        <v>-1.0939</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0107</v>
+        <v>-0.9908</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9822</v>
+        <v>-0.1768</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0285</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7019</v>
+        <v>-4.1754</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1915</v>
+        <v>-0.7721</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5104</v>
+        <v>-3.4033</v>
       </c>
       <c r="G9" t="n">
         <v>-4.1638</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5031</v>
+        <v>-0.9766</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5658</v>
+        <v>-0.1464</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9373</v>
+        <v>-0.8302</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7921</v>
+        <v>-4.6652</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9513</v>
+        <v>-1.8512</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8408</v>
+        <v>-2.8141</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5675</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9617</v>
+        <v>-0.8348</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7733</v>
+        <v>-0.6732</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1884</v>
+        <v>-0.1616</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4559</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.8712</v>
+        <v>-14.9788</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6082</v>
+        <v>5.500399999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-20.4793</v>
@@ -1288,10 +1288,10 @@
         <v>11.7092</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4114</v>
+        <v>5.411400000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>6.2978</v>
+        <v>6.297800000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-28.7026</v>
@@ -1312,16 +1312,16 @@
         <v>16.4056</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.204599999999999</v>
+        <v>-6.3123</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.0666</v>
+        <v>-2.1744</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.1379</v>
+        <v>-4.138</v>
       </c>
       <c r="V11" t="n">
-        <v>4.466899999999999</v>
+        <v>4.466900000000001</v>
       </c>
       <c r="W11" t="n">
         <v>8.5113</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5054</v>
+        <v>5.1792</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5637</v>
+        <v>4.5103</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0583</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3165</v>
+        <v>4.4149</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1151</v>
+        <v>3.2168</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2014</v>
+        <v>1.1981</v>
       </c>
       <c r="J12" t="n">
-        <v>1.672</v>
+        <v>5.7491</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4278</v>
+        <v>3.8448</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2442</v>
+        <v>1.9043</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9885</v>
+        <v>-1.3342</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5429</v>
+        <v>-0.628</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4456</v>
+        <v>-0.7062</v>
       </c>
       <c r="P12" t="n">
-        <v>0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.158</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2428</v>
+        <v>0.9802</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5938</v>
+        <v>0.4283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.649</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.614</v>
+        <v>0.9421</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.842</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0076</v>
+        <v>4.8692</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7336</v>
+        <v>6.4345</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.726</v>
+        <v>-1.5653</v>
       </c>
       <c r="G13" t="n">
         <v>4.2448</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>0.033</v>
+        <v>0.8946</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3873</v>
+        <v>0.3137</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4204</v>
+        <v>0.581</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6562</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8433</v>
+        <v>3.5235</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7092</v>
+        <v>4.2618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1341</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4149</v>
+        <v>-0.3165</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2168</v>
+        <v>-0.1151</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1981</v>
+        <v>-0.2014</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7491</v>
+        <v>1.672</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8448</v>
+        <v>1.4278</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9043</v>
+        <v>0.2442</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3342</v>
+        <v>-1.9885</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.628</v>
+        <v>-1.5429</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7062</v>
+        <v>-0.4456</v>
       </c>
       <c r="P14" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-1.158</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3556</v>
+        <v>2.2609</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3728</v>
+        <v>1.2919</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0172</v>
+        <v>0.969</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9421</v>
+        <v>0.614</v>
       </c>
       <c r="W14" t="n">
-        <v>1.228</v>
+        <v>2.4559</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4222</v>
+        <v>3.1872</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8725</v>
+        <v>2.1729</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5497</v>
+        <v>1.0143</v>
       </c>
       <c r="G15" t="n">
         <v>0.8668</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9763</v>
+        <v>1.7414</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2353</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.741</v>
+        <v>1.2056</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6906</v>
+        <v>1.9045</v>
       </c>
       <c r="E16" t="n">
         <v>-1.2901</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9807</v>
+        <v>3.1946</v>
       </c>
       <c r="G16" t="n">
         <v>1.3106</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3801</v>
+        <v>0.5939</v>
       </c>
       <c r="T16" t="n">
         <v>0.2062</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1738</v>
+        <v>0.3876</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6094</v>
+        <v>1.0694</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1104</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.501</v>
+        <v>0.0931</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0724</v>
+        <v>0.1563</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7428</v>
+        <v>0.0177</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6705</v>
+        <v>0.1385</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8392</v>
+        <v>0.8368</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6764</v>
+        <v>0.1449</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>0.6919</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7669</v>
+        <v>-0.6805</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0664</v>
+        <v>-0.1272</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8333</v>
+        <v>-0.5534</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6987</v>
+        <v>0.5271</v>
       </c>
       <c r="T17" t="n">
-        <v>1.363</v>
+        <v>0.1395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3357</v>
+        <v>0.3876</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3547</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6625</v>
+        <v>1.0281</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0628</v>
+        <v>1.2092</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4002</v>
+        <v>-0.1811</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4462</v>
+        <v>1.0724</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06</v>
+        <v>1.7428</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5062</v>
+        <v>-0.6705</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4547</v>
+        <v>1.8392</v>
       </c>
       <c r="K18" t="n">
-        <v>0.414</v>
+        <v>1.6764</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>0.1628</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9009</v>
+        <v>-0.7669</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3539</v>
+        <v>0.0664</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.8333</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3946</v>
+        <v>1.1174</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6081</v>
+        <v>0.4617</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2135</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3281</v>
+        <v>-1.3547</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3281</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0123</v>
+        <v>0.4758</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3754</v>
+        <v>0.6622</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3877</v>
+        <v>-0.1864</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1563</v>
+        <v>-0.4462</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0177</v>
+        <v>0.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1385</v>
+        <v>-0.5062</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8368</v>
+        <v>0.4547</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1449</v>
+        <v>0.414</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6919</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6805</v>
+        <v>-0.9009</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1272</v>
+        <v>-0.3539</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5534</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P19" t="n">
         <v>0.386</v>
@@ -1936,22 +1936,22 @@
         <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5546</v>
+        <v>0.2079</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4614</v>
+        <v>0.2076</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.0003</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8259</v>
+        <v>-1.1246</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0801</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7458</v>
+        <v>-0.3449</v>
       </c>
       <c r="G20" t="n">
         <v>0.7422</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1038</v>
+        <v>0.8051</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0462</v>
+        <v>0.2542</v>
       </c>
       <c r="U20" t="n">
-        <v>0.15</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0317</v>
+        <v>-1.5706</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4221</v>
+        <v>2.322</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4538</v>
+        <v>-3.8926</v>
       </c>
       <c r="G21" t="n">
         <v>4.9483</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2855</v>
+        <v>0.7466</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3993</v>
+        <v>0.2991</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1137</v>
+        <v>0.4475</v>
       </c>
       <c r="V21" t="n">
         <v>-2.8263</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>15.8711</v>
+        <v>18.5417</v>
       </c>
       <c r="E22" t="n">
-        <v>20.47949999999999</v>
+        <v>20.4794</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6083</v>
+        <v>-1.9378</v>
       </c>
       <c r="G22" t="n">
         <v>16.9936</v>
@@ -2140,7 +2140,7 @@
         <v>13.6874</v>
       </c>
       <c r="I22" t="n">
-        <v>3.3058</v>
+        <v>3.305800000000001</v>
       </c>
       <c r="J22" t="n">
         <v>28.7027</v>
@@ -2170,13 +2170,13 @@
         <v>12.5455</v>
       </c>
       <c r="S22" t="n">
-        <v>7.204599999999999</v>
+        <v>9.8751</v>
       </c>
       <c r="T22" t="n">
         <v>4.138</v>
       </c>
       <c r="U22" t="n">
-        <v>3.0667</v>
+        <v>5.7371</v>
       </c>
       <c r="V22" t="n">
         <v>-4.466799999999999</v>
